--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2381,6 +2381,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2398,6 +2398,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2415,6 +2415,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2432,6 +2432,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2449,6 +2449,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2466,6 +2466,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2483,6 +2483,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2500,6 +2500,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2517,6 +2517,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2534,6 +2534,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2551,6 +2551,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2568,6 +2568,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2585,6 +2585,27 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>10.479</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>-147</v>
+      </c>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2606,6 +2606,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2623,6 +2623,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2640,6 +2640,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2657,6 +2657,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2674,6 +2674,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2691,6 +2691,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>-140</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2714,6 +2714,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>-145</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2737,6 +2737,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>10.479</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>-147</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2760,6 +2760,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2777,6 +2777,27 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>10.479</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>-147</v>
+      </c>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2798,6 +2798,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>10.179</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>-148</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2821,6 +2821,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>10.179</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>-148</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2844,6 +2844,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>10.479</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>-147</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2867,6 +2867,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>10.479</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>-147</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2890,6 +2890,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>10.479</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>-147</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2913,6 +2913,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>12.406</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>-141</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2936,6 +2936,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>13.099</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>-139</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2959,6 +2959,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>14.207</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>-136</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2982,6 +2982,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2999,6 +2999,27 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>-135</v>
+      </c>
+      <c r="D121" s="5" t="n"/>
+      <c r="E121" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3020,6 +3020,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>13.826</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>-137</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3043,6 +3043,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>-135</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3066,6 +3066,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>14.207</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>-136</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3089,6 +3089,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>13.458</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>-138</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3112,6 +3112,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>13.458</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>-138</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3135,6 +3135,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>13.826</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>-137</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3158,6 +3158,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>14.207</v>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>-136</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3181,6 +3181,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>-135</v>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3204,6 +3204,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>15.412</v>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>-133</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3227,6 +3227,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>15.412</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>-133</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3250,6 +3250,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>15.412</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>-133</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3273,6 +3273,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>14.207</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>-136</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3296,6 +3296,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>14.994</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>-134</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3319,6 +3319,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>-135</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3342,6 +3342,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>-135</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
